--- a/exports/trend_1d/PNB_full_report.xlsx
+++ b/exports/trend_1d/PNB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q94"/>
+  <dimension ref="A1:U94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42033</v>
+        <v>42034</v>
       </c>
       <c r="H2" t="n">
-        <v>188.02</v>
+        <v>179.1</v>
       </c>
       <c r="I2" t="n">
         <v>184.68547246</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.21</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>5.59</v>
+        <v>10.49</v>
       </c>
       <c r="M2" t="n">
         <v>0.38</v>
       </c>
       <c r="N2" t="n">
-        <v>3.68</v>
+        <v>4.74</v>
       </c>
       <c r="O2" t="n">
         <v>3.45</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.29</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42103</v>
+        <v>42104</v>
       </c>
       <c r="H3" t="n">
-        <v>152.93</v>
+        <v>154.5</v>
       </c>
       <c r="I3" t="n">
         <v>154.4048252138897</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
-        <v>14.61</v>
+        <v>13.74</v>
       </c>
       <c r="L3" t="n">
         <v>6.67</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.08</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42131</v>
+        <v>42132</v>
       </c>
       <c r="H4" t="n">
-        <v>147.27</v>
+        <v>137.59</v>
       </c>
       <c r="I4" t="n">
         <v>142.8245688316132</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.68</v>
+        <v>-10.94</v>
       </c>
       <c r="L4" t="n">
-        <v>6.78</v>
+        <v>13.02</v>
       </c>
       <c r="M4" t="n">
         <v>0.63</v>
       </c>
       <c r="N4" t="n">
-        <v>3.53</v>
+        <v>6.57</v>
       </c>
       <c r="O4" t="n">
         <v>1.03</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>17.92</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42214</v>
+        <v>42215</v>
       </c>
       <c r="H5" t="n">
-        <v>129.99</v>
+        <v>142.69</v>
       </c>
       <c r="I5" t="n">
         <v>137.5665258440536</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K5" t="n">
-        <v>5.52</v>
+        <v>-3.71</v>
       </c>
       <c r="L5" t="n">
         <v>9.859999999999999</v>
@@ -726,7 +785,7 @@
         <v>1.6</v>
       </c>
       <c r="N5" t="n">
-        <v>4.96</v>
+        <v>9.77</v>
       </c>
       <c r="O5" t="n">
         <v>-6.57</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>15.44</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>150.48</v>
+        <v>134.66</v>
       </c>
       <c r="I6" t="n">
         <v>142.3479849563707</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>5.46</v>
+        <v>-5.63</v>
       </c>
       <c r="L6" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>2.51</v>
+        <v>4.29</v>
       </c>
       <c r="N6" t="n">
-        <v>5.36</v>
+        <v>10.51</v>
       </c>
       <c r="O6" t="n">
         <v>9.77</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>22.05</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42321</v>
+        <v>42324</v>
       </c>
       <c r="H7" t="n">
-        <v>129.24</v>
+        <v>132.35</v>
       </c>
       <c r="I7" t="n">
         <v>131.4432081292519</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>4.02</v>
+        <v>1.72</v>
       </c>
       <c r="L7" t="n">
         <v>7.95</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42345</v>
+        <v>42346</v>
       </c>
       <c r="H8" t="n">
-        <v>126.45</v>
+        <v>124.57</v>
       </c>
       <c r="I8" t="n">
         <v>126.1906926909402</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.46</v>
+        <v>-5.88</v>
       </c>
       <c r="L8" t="n">
-        <v>5.1</v>
+        <v>6.38</v>
       </c>
       <c r="M8" t="n">
         <v>0.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42446</v>
+        <v>42447</v>
       </c>
       <c r="H9" t="n">
-        <v>78.15000000000001</v>
+        <v>79.61</v>
       </c>
       <c r="I9" t="n">
         <v>79.33960646890165</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K9" t="n">
-        <v>37.26</v>
+        <v>36.09</v>
       </c>
       <c r="L9" t="n">
         <v>2.34</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.45</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H10" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73</v>
       </c>
       <c r="I10" t="n">
         <v>76.81553047497837</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.66</v>
+        <v>-3.62</v>
       </c>
       <c r="L10" t="n">
         <v>5.21</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.6</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42528</v>
+        <v>42529</v>
       </c>
       <c r="H11" t="n">
-        <v>73.33</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>75.6444548077875</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.43</v>
+        <v>0.68</v>
       </c>
       <c r="L11" t="n">
         <v>3.08</v>
@@ -1068,7 +1199,7 @@
         <v>1.82</v>
       </c>
       <c r="N11" t="n">
-        <v>3.33</v>
+        <v>3.93</v>
       </c>
       <c r="O11" t="n">
         <v>-1.99</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.06</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42572</v>
+        <v>42573</v>
       </c>
       <c r="H12" t="n">
-        <v>116.77</v>
+        <v>113.52</v>
       </c>
       <c r="I12" t="n">
         <v>114.0186601853715</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>53.22</v>
+        <v>48.96</v>
       </c>
       <c r="L12" t="n">
         <v>4.09</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.43</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42615</v>
+        <v>42619</v>
       </c>
       <c r="H13" t="n">
-        <v>119.14</v>
+        <v>125.32</v>
       </c>
       <c r="I13" t="n">
         <v>124.045743241205</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.95</v>
+        <v>-10.39</v>
       </c>
       <c r="L13" t="n">
         <v>13.64</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.58</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H14" t="n">
-        <v>129.1</v>
+        <v>125.74</v>
       </c>
       <c r="I14" t="n">
         <v>126.0250852822044</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K14" t="n">
-        <v>3.02</v>
+        <v>0.34</v>
       </c>
       <c r="L14" t="n">
         <v>4.07</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>12.03</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H15" t="n">
-        <v>134.29</v>
+        <v>150.44</v>
       </c>
       <c r="I15" t="n">
         <v>136.605170979286</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.8</v>
+        <v>-19.64</v>
       </c>
       <c r="L15" t="n">
-        <v>8.529999999999999</v>
+        <v>21.22</v>
       </c>
       <c r="M15" t="n">
         <v>5.66</v>
       </c>
       <c r="N15" t="n">
-        <v>6.68</v>
+        <v>12.03</v>
       </c>
       <c r="O15" t="n">
         <v>-2.6</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>17.57</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42702</v>
+        <v>42703</v>
       </c>
       <c r="H16" t="n">
-        <v>129.48</v>
+        <v>128.53</v>
       </c>
       <c r="I16" t="n">
         <v>128.6726817384414</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>-13.93</v>
+        <v>-14.56</v>
       </c>
       <c r="L16" t="n">
         <v>16.17</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>15.64</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42746</v>
+        <v>42747</v>
       </c>
       <c r="H17" t="n">
-        <v>116.73</v>
+        <v>118.99</v>
       </c>
       <c r="I17" t="n">
         <v>118.2278134108254</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K17" t="n">
-        <v>9.18</v>
+        <v>7.42</v>
       </c>
       <c r="L17" t="n">
         <v>2.5</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42815</v>
+        <v>42816</v>
       </c>
       <c r="H18" t="n">
-        <v>134.91</v>
+        <v>128.81</v>
       </c>
       <c r="I18" t="n">
         <v>129.5342328175331</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K18" t="n">
-        <v>13.38</v>
+        <v>8.25</v>
       </c>
       <c r="L18" t="n">
         <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>0.59</v>
+        <v>1.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>4.52</v>
       </c>
       <c r="O18" t="n">
         <v>1.94</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>10.42</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42821</v>
+        <v>42822</v>
       </c>
       <c r="H19" t="n">
-        <v>139.06</v>
+        <v>140.52</v>
       </c>
       <c r="I19" t="n">
         <v>139.5363821172332</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.96</v>
+        <v>-9.09</v>
       </c>
       <c r="L19" t="n">
-        <v>8.73</v>
+        <v>9.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="N19" t="n">
         <v>4.16</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="H20" t="n">
-        <v>155.87</v>
+        <v>149.69</v>
       </c>
       <c r="I20" t="n">
         <v>151.157986801256</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K20" t="n">
-        <v>10.92</v>
+        <v>6.53</v>
       </c>
       <c r="L20" t="n">
         <v>1.81</v>
       </c>
       <c r="M20" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>5.23</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>15.29</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42923</v>
+        <v>42926</v>
       </c>
       <c r="H21" t="n">
-        <v>136.18</v>
+        <v>144.72</v>
       </c>
       <c r="I21" t="n">
         <v>140.8420729190931</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K21" t="n">
-        <v>9.029999999999999</v>
+        <v>3.32</v>
       </c>
       <c r="L21" t="n">
         <v>3.72</v>
@@ -1638,7 +1889,7 @@
         <v>2.81</v>
       </c>
       <c r="N21" t="n">
-        <v>4.91</v>
+        <v>6.27</v>
       </c>
       <c r="O21" t="n">
         <v>-3.96</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.96</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42949</v>
+        <v>42950</v>
       </c>
       <c r="H22" t="n">
-        <v>150.11</v>
+        <v>141</v>
       </c>
       <c r="I22" t="n">
         <v>141.1630749318026</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
-        <v>3.72</v>
+        <v>-2.57</v>
       </c>
       <c r="L22" t="n">
         <v>5.31</v>
@@ -1695,7 +1958,7 @@
         <v>2.49</v>
       </c>
       <c r="N22" t="n">
-        <v>2.99</v>
+        <v>6.07</v>
       </c>
       <c r="O22" t="n">
         <v>6.27</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>14.63</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H23" t="n">
-        <v>130.51</v>
+        <v>190.81</v>
       </c>
       <c r="I23" t="n">
         <v>133.4067278654365</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K23" t="n">
-        <v>7.44</v>
+        <v>-35.33</v>
       </c>
       <c r="L23" t="n">
-        <v>5.72</v>
+        <v>38.34</v>
       </c>
       <c r="M23" t="n">
-        <v>1.39</v>
+        <v>9.99</v>
       </c>
       <c r="N23" t="n">
-        <v>5.5</v>
+        <v>46.2</v>
       </c>
       <c r="O23" t="n">
         <v>-6.07</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>27.59</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43068</v>
+        <v>43069</v>
       </c>
       <c r="H24" t="n">
-        <v>171.5</v>
+        <v>166.3</v>
       </c>
       <c r="I24" t="n">
         <v>167.630451613633</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K24" t="n">
-        <v>-10.12</v>
+        <v>-12.85</v>
       </c>
       <c r="L24" t="n">
         <v>24.77</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>13.56</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43122</v>
+        <v>43123</v>
       </c>
       <c r="H25" t="n">
-        <v>166.21</v>
+        <v>175.47</v>
       </c>
       <c r="I25" t="n">
         <v>173.5331821793248</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05</v>
+        <v>-5.51</v>
       </c>
       <c r="L25" t="n">
-        <v>3.78</v>
+        <v>6.64</v>
       </c>
       <c r="M25" t="n">
         <v>2.93</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>14.49</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H26" t="n">
-        <v>158.23</v>
+        <v>152.85</v>
       </c>
       <c r="I26" t="n">
         <v>155.4172839432357</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.83</v>
+        <v>-12.89</v>
       </c>
       <c r="L26" t="n">
-        <v>10.66</v>
+        <v>13.62</v>
       </c>
       <c r="M26" t="n">
-        <v>0.67</v>
+        <v>1.52</v>
       </c>
       <c r="N26" t="n">
         <v>7.06</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>17.36</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43245</v>
+        <v>43248</v>
       </c>
       <c r="H27" t="n">
-        <v>78.70999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>82.5491092971609</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K27" t="n">
-        <v>48.51</v>
+        <v>45.2</v>
       </c>
       <c r="L27" t="n">
         <v>4.23</v>
@@ -1980,7 +2303,7 @@
         <v>1.8</v>
       </c>
       <c r="N27" t="n">
-        <v>5.29</v>
+        <v>6.42</v>
       </c>
       <c r="O27" t="n">
         <v>-3.4</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>16.39</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43273</v>
+        <v>43276</v>
       </c>
       <c r="H28" t="n">
-        <v>77.34</v>
+        <v>75.36</v>
       </c>
       <c r="I28" t="n">
         <v>77.09534829869145</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.66</v>
+        <v>-10.03</v>
       </c>
       <c r="L28" t="n">
-        <v>8.619999999999999</v>
+        <v>10.36</v>
       </c>
       <c r="M28" t="n">
         <v>1.22</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.98</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H29" t="n">
-        <v>77.44</v>
+        <v>81.12</v>
       </c>
       <c r="I29" t="n">
         <v>78.19402503990763</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.76</v>
+        <v>-7.64</v>
       </c>
       <c r="L29" t="n">
-        <v>5.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>1.84</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>12.52</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43360</v>
+        <v>43361</v>
       </c>
       <c r="H30" t="n">
-        <v>78.38</v>
+        <v>74.89</v>
       </c>
       <c r="I30" t="n">
         <v>75.06056018333268</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.38</v>
+        <v>-7.68</v>
       </c>
       <c r="L30" t="n">
-        <v>8.43</v>
+        <v>8.49</v>
       </c>
       <c r="M30" t="n">
         <v>1.48</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.23</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43447</v>
+        <v>43448</v>
       </c>
       <c r="H31" t="n">
-        <v>67.38</v>
+        <v>68.61</v>
       </c>
       <c r="I31" t="n">
         <v>68.41806151397991</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K31" t="n">
-        <v>10.03</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>4.15</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.09</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H32" t="n">
-        <v>73.76000000000001</v>
+        <v>72.34</v>
       </c>
       <c r="I32" t="n">
         <v>72.41835732660255</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K32" t="n">
-        <v>7.51</v>
+        <v>5.44</v>
       </c>
       <c r="L32" t="n">
         <v>2.54</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>12.2</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H33" t="n">
-        <v>72.39</v>
+        <v>78.05</v>
       </c>
       <c r="I33" t="n">
         <v>74.15531375015944</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-7.89</v>
       </c>
       <c r="L33" t="n">
-        <v>5.02</v>
+        <v>8.81</v>
       </c>
       <c r="M33" t="n">
         <v>6.88</v>
       </c>
       <c r="N33" t="n">
-        <v>6.03</v>
+        <v>7.82</v>
       </c>
       <c r="O33" t="n">
         <v>-1.93</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.97</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H34" t="n">
-        <v>85.04000000000001</v>
+        <v>81.83</v>
       </c>
       <c r="I34" t="n">
         <v>83.43306156825608</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K34" t="n">
-        <v>8.960000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="L34" t="n">
         <v>7.74</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.23</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43768</v>
+        <v>43769</v>
       </c>
       <c r="H35" t="n">
-        <v>60.16</v>
+        <v>61.72</v>
       </c>
       <c r="I35" t="n">
         <v>60.52135152421827</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K35" t="n">
-        <v>26.48</v>
+        <v>24.58</v>
       </c>
       <c r="L35" t="n">
         <v>5.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>10.29</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43776</v>
+        <v>43777</v>
       </c>
       <c r="H36" t="n">
-        <v>58.51</v>
+        <v>58.03</v>
       </c>
       <c r="I36" t="n">
         <v>58.04766546299683</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.2</v>
+        <v>-5.98</v>
       </c>
       <c r="L36" t="n">
-        <v>5.52</v>
+        <v>6.51</v>
       </c>
       <c r="M36" t="n">
         <v>0.46</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>12.72</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43796</v>
+        <v>43797</v>
       </c>
       <c r="H37" t="n">
-        <v>60.16</v>
+        <v>63.22</v>
       </c>
       <c r="I37" t="n">
         <v>63.13162699531154</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.67</v>
+        <v>-8.94</v>
       </c>
       <c r="L37" t="n">
-        <v>6.36</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>5.09</v>
       </c>
       <c r="O37" t="n">
         <v>-0.82</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>11.51</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43808</v>
+        <v>43809</v>
       </c>
       <c r="H38" t="n">
-        <v>57.42</v>
+        <v>56.33</v>
       </c>
       <c r="I38" t="n">
         <v>56.6033139860203</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.17</v>
+        <v>-10.9</v>
       </c>
       <c r="L38" t="n">
-        <v>11.06</v>
+        <v>11.26</v>
       </c>
       <c r="M38" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="N38" t="n">
         <v>4.33</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.31</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H39" t="n">
-        <v>61.1</v>
+        <v>62.99</v>
       </c>
       <c r="I39" t="n">
         <v>62.48813635703387</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.470000000000001</v>
+        <v>-11.82</v>
       </c>
       <c r="L39" t="n">
-        <v>11.41</v>
+        <v>12.32</v>
       </c>
       <c r="M39" t="n">
         <v>0.79</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H40" t="n">
-        <v>57.56</v>
+        <v>56.61</v>
       </c>
       <c r="I40" t="n">
         <v>56.87794356964876</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.619999999999999</v>
+        <v>-10.13</v>
       </c>
       <c r="L40" t="n">
-        <v>9.81</v>
+        <v>10.57</v>
       </c>
       <c r="M40" t="n">
         <v>1.39</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.9</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43985</v>
+        <v>43986</v>
       </c>
       <c r="H41" t="n">
-        <v>28.57</v>
+        <v>29.28</v>
       </c>
       <c r="I41" t="n">
         <v>28.95364509041811</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K41" t="n">
-        <v>49.53</v>
+        <v>48.28</v>
       </c>
       <c r="L41" t="n">
         <v>2.19</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>15.67</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44036</v>
+        <v>44039</v>
       </c>
       <c r="H42" t="n">
-        <v>31.69</v>
+        <v>30.5</v>
       </c>
       <c r="I42" t="n">
         <v>30.92466979454507</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K42" t="n">
-        <v>8.23</v>
+        <v>4.17</v>
       </c>
       <c r="L42" t="n">
         <v>4.23</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>13.85</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44063</v>
+        <v>44064</v>
       </c>
       <c r="H43" t="n">
-        <v>33.15</v>
+        <v>33.67</v>
       </c>
       <c r="I43" t="n">
         <v>33.44547895449479</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.69</v>
+        <v>-10.39</v>
       </c>
       <c r="L43" t="n">
-        <v>9.15</v>
+        <v>13.64</v>
       </c>
       <c r="M43" t="n">
         <v>4.29</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.51</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44091</v>
+        <v>44092</v>
       </c>
       <c r="H44" t="n">
-        <v>31.4</v>
+        <v>30.78</v>
       </c>
       <c r="I44" t="n">
         <v>30.88570230505339</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.74</v>
+        <v>-8.58</v>
       </c>
       <c r="L44" t="n">
-        <v>8.699999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="M44" t="n">
         <v>2.03</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.21</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H45" t="n">
-        <v>27</v>
+        <v>27.96</v>
       </c>
       <c r="I45" t="n">
         <v>27.48501507191019</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K45" t="n">
-        <v>12.28</v>
+        <v>9.16</v>
       </c>
       <c r="L45" t="n">
         <v>2.63</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.81</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H46" t="n">
-        <v>34.52</v>
+        <v>32.2</v>
       </c>
       <c r="I46" t="n">
         <v>33.52699486534789</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K46" t="n">
-        <v>23.46</v>
+        <v>15.16</v>
       </c>
       <c r="L46" t="n">
         <v>4.26</v>
@@ -3063,7 +3614,7 @@
         <v>2.5</v>
       </c>
       <c r="N46" t="n">
-        <v>6.54</v>
+        <v>6.72</v>
       </c>
       <c r="O46" t="n">
         <v>3.56</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>20.91</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H47" t="n">
-        <v>34.19</v>
+        <v>36.22</v>
       </c>
       <c r="I47" t="n">
         <v>35.14351952533852</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.18</v>
+        <v>-12.48</v>
       </c>
       <c r="L47" t="n">
-        <v>10.87</v>
+        <v>13.66</v>
       </c>
       <c r="M47" t="n">
         <v>1.73</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>17.24</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H48" t="n">
-        <v>36.6</v>
+        <v>34.94</v>
       </c>
       <c r="I48" t="n">
         <v>35.48755426603726</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K48" t="n">
-        <v>1.05</v>
+        <v>-3.53</v>
       </c>
       <c r="L48" t="n">
         <v>6.93</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>16.95</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H49" t="n">
-        <v>35.94</v>
+        <v>37.59</v>
       </c>
       <c r="I49" t="n">
         <v>36.16909330228251</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.86</v>
+        <v>-7.58</v>
       </c>
       <c r="L49" t="n">
-        <v>5.95</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
         <v>8.56</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>13.28</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44404</v>
+        <v>44405</v>
       </c>
       <c r="H50" t="n">
-        <v>36.97</v>
+        <v>36.27</v>
       </c>
       <c r="I50" t="n">
         <v>36.63631573045224</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.65</v>
+        <v>-3.51</v>
       </c>
       <c r="L50" t="n">
-        <v>2.63</v>
+        <v>4.28</v>
       </c>
       <c r="M50" t="n">
         <v>1.97</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.02</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H51" t="n">
-        <v>36.6</v>
+        <v>39.47</v>
       </c>
       <c r="I51" t="n">
         <v>36.61726608341411</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.91</v>
+        <v>-8.82</v>
       </c>
       <c r="L51" t="n">
-        <v>8.050000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="M51" t="n">
         <v>1.98</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>7.84</v>
       </c>
       <c r="O51" t="n">
         <v>-1.89</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11.72</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H52" t="n">
-        <v>39.34</v>
+        <v>37.68</v>
       </c>
       <c r="I52" t="n">
         <v>38.29698260670897</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.33</v>
+        <v>-4.54</v>
       </c>
       <c r="L52" t="n">
         <v>10.64</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.16</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H53" t="n">
-        <v>36.73</v>
+        <v>38.1</v>
       </c>
       <c r="I53" t="n">
         <v>37.93146980451349</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>2.52</v>
+        <v>-1.11</v>
       </c>
       <c r="L53" t="n">
         <v>4.75</v>
@@ -3462,7 +4097,7 @@
         <v>1.25</v>
       </c>
       <c r="N53" t="n">
-        <v>3.14</v>
+        <v>3.73</v>
       </c>
       <c r="O53" t="n">
         <v>-4.22</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H54" t="n">
-        <v>37.54</v>
+        <v>35.04</v>
       </c>
       <c r="I54" t="n">
         <v>36.59526751383929</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.47</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>7.53</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>1.11</v>
+        <v>4.16</v>
       </c>
       <c r="N54" t="n">
-        <v>2.99</v>
+        <v>6.66</v>
       </c>
       <c r="O54" t="n">
         <v>3.73</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>13.6</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H55" t="n">
-        <v>28.62</v>
+        <v>29.61</v>
       </c>
       <c r="I55" t="n">
         <v>29.4881609086302</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K55" t="n">
-        <v>18.32</v>
+        <v>15.5</v>
       </c>
       <c r="L55" t="n">
         <v>5.39</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>6</v>
+      </c>
+      <c r="U55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H56" t="n">
-        <v>36.03</v>
+        <v>34</v>
       </c>
       <c r="I56" t="n">
         <v>34.96665212609473</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K56" t="n">
-        <v>21.68</v>
+        <v>14.83</v>
       </c>
       <c r="L56" t="n">
         <v>3.17</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>15.02</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H57" t="n">
-        <v>37.16</v>
+        <v>38.25</v>
       </c>
       <c r="I57" t="n">
         <v>37.42398105771048</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>-9.289999999999999</v>
+        <v>-12.5</v>
       </c>
       <c r="L57" t="n">
-        <v>11.38</v>
+        <v>13.18</v>
       </c>
       <c r="M57" t="n">
         <v>2.54</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.78</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H58" t="n">
-        <v>52.46</v>
+        <v>50.19</v>
       </c>
       <c r="I58" t="n">
         <v>50.33551752595091</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K58" t="n">
-        <v>37.15</v>
+        <v>31.22</v>
       </c>
       <c r="L58" t="n">
         <v>4.71</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>17.78</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45040</v>
+        <v>45041</v>
       </c>
       <c r="H59" t="n">
-        <v>46.51</v>
+        <v>47.03</v>
       </c>
       <c r="I59" t="n">
         <v>46.61627659193651</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K59" t="n">
-        <v>7.33</v>
+        <v>6.3</v>
       </c>
       <c r="L59" t="n">
         <v>11.87</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45055</v>
+        <v>45056</v>
       </c>
       <c r="H60" t="n">
-        <v>47.45</v>
+        <v>45.8</v>
       </c>
       <c r="I60" t="n">
         <v>46.93248535383155</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>0.89</v>
+        <v>-2.62</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>3.83</v>
       </c>
       <c r="M60" t="n">
         <v>1.62</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>10.03</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45097</v>
+        <v>45098</v>
       </c>
       <c r="H61" t="n">
-        <v>49.01</v>
+        <v>49.91</v>
       </c>
       <c r="I61" t="n">
         <v>49.54066835107441</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.01</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>8.859999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M61" t="n">
         <v>1.23</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.9</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45218</v>
+        <v>45219</v>
       </c>
       <c r="H62" t="n">
-        <v>69.89</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>69.1332999740826</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K62" t="n">
-        <v>40.03</v>
+        <v>36.73</v>
       </c>
       <c r="L62" t="n">
         <v>5.95</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>11.45</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45242</v>
+        <v>45243</v>
       </c>
       <c r="H63" t="n">
-        <v>72.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I63" t="n">
         <v>72.64586229608935</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.66</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>6.36</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M63" t="n">
         <v>2.8</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H64" t="n">
-        <v>113.94</v>
+        <v>111.2</v>
       </c>
       <c r="I64" t="n">
         <v>111.8647039145627</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K64" t="n">
-        <v>52.53</v>
+        <v>48.86</v>
       </c>
       <c r="L64" t="n">
         <v>4.43</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>13.19</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H65" t="n">
-        <v>119.65</v>
+        <v>127.63</v>
       </c>
       <c r="I65" t="n">
         <v>123.3675705997721</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.6</v>
+        <v>-14.78</v>
       </c>
       <c r="L65" t="n">
-        <v>7.85</v>
+        <v>16.1</v>
       </c>
       <c r="M65" t="n">
         <v>1.62</v>
       </c>
       <c r="N65" t="n">
-        <v>3.77</v>
+        <v>6.67</v>
       </c>
       <c r="O65" t="n">
         <v>-2.4</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>12.75</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H66" t="n">
-        <v>128.25</v>
+        <v>120.03</v>
       </c>
       <c r="I66" t="n">
         <v>120.2047148239826</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K66" t="n">
-        <v>0.49</v>
+        <v>-5.95</v>
       </c>
       <c r="L66" t="n">
         <v>7.33</v>
@@ -4203,7 +4994,7 @@
         <v>1.96</v>
       </c>
       <c r="N66" t="n">
-        <v>3.24</v>
+        <v>6.41</v>
       </c>
       <c r="O66" t="n">
         <v>6.67</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>15.21</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H67" t="n">
-        <v>122.25</v>
+        <v>129.38</v>
       </c>
       <c r="I67" t="n">
         <v>129.0227536836246</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.85</v>
+        <v>-7.79</v>
       </c>
       <c r="L67" t="n">
-        <v>7.71</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>1.43</v>
+        <v>4.29</v>
       </c>
       <c r="N67" t="n">
-        <v>2.45</v>
+        <v>5.83</v>
       </c>
       <c r="O67" t="n">
         <v>-6.41</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>10.31</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H68" t="n">
-        <v>129.38</v>
+        <v>108.93</v>
       </c>
       <c r="I68" t="n">
         <v>116.0363326243392</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>-15.81</v>
       </c>
       <c r="L68" t="n">
-        <v>3.18</v>
+        <v>23.94</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>15.81</v>
       </c>
       <c r="O68" t="n">
         <v>5.83</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>22.78</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45499</v>
+        <v>45502</v>
       </c>
       <c r="H69" t="n">
-        <v>113.28</v>
+        <v>119.93</v>
       </c>
       <c r="I69" t="n">
         <v>119.4349037154412</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.99</v>
+        <v>-10.1</v>
       </c>
       <c r="L69" t="n">
         <v>18.25</v>
       </c>
       <c r="M69" t="n">
-        <v>3.17</v>
+        <v>4.09</v>
       </c>
       <c r="N69" t="n">
-        <v>5.64</v>
+        <v>5.87</v>
       </c>
       <c r="O69" t="n">
         <v>-15.81</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>10.06</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H70" t="n">
-        <v>113.57</v>
+        <v>107.6</v>
       </c>
       <c r="I70" t="n">
         <v>108.3170415550692</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K70" t="n">
-        <v>-5.3</v>
+        <v>-10.28</v>
       </c>
       <c r="L70" t="n">
-        <v>5.85</v>
+        <v>10.86</v>
       </c>
       <c r="M70" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="N70" t="n">
-        <v>2.19</v>
+        <v>5.26</v>
       </c>
       <c r="O70" t="n">
         <v>5.87</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>12.23</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="H71" t="n">
-        <v>97.88</v>
+        <v>98.88</v>
       </c>
       <c r="I71" t="n">
         <v>98.85202049673072</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K71" t="n">
-        <v>9.029999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="L71" t="n">
         <v>3.55</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>11.81</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="H72" t="n">
-        <v>95.25</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>91.11648826994309</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.67</v>
+        <v>-7.96</v>
       </c>
       <c r="L72" t="n">
-        <v>6.47</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M72" t="n">
         <v>1.13</v>
       </c>
       <c r="N72" t="n">
-        <v>3.05</v>
+        <v>4.45</v>
       </c>
       <c r="O72" t="n">
         <v>1.02</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>12.77</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H73" t="n">
-        <v>101.97</v>
+        <v>103.89</v>
       </c>
       <c r="I73" t="n">
         <v>102.6309511005399</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K73" t="n">
-        <v>-12.04</v>
+        <v>-14.15</v>
       </c>
       <c r="L73" t="n">
-        <v>12.38</v>
+        <v>14.67</v>
       </c>
       <c r="M73" t="n">
         <v>3.29</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H74" t="n">
-        <v>97.76000000000001</v>
+        <v>95.16</v>
       </c>
       <c r="I74" t="n">
         <v>95.26341648366716</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.9</v>
+        <v>-8.4</v>
       </c>
       <c r="L74" t="n">
         <v>9.49</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>10.52</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H75" t="n">
-        <v>87.95999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I75" t="n">
         <v>89.66260032528723</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K75" t="n">
-        <v>7.57</v>
+        <v>4.79</v>
       </c>
       <c r="L75" t="n">
         <v>6.43</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.83</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="H76" t="n">
-        <v>93.87</v>
+        <v>89.22</v>
       </c>
       <c r="I76" t="n">
         <v>90.10150278261224</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K76" t="n">
-        <v>3.61</v>
+        <v>-1.52</v>
       </c>
       <c r="L76" t="n">
         <v>6.1</v>
@@ -4773,7 +5684,7 @@
         <v>5.83</v>
       </c>
       <c r="N76" t="n">
-        <v>3.33</v>
+        <v>4.95</v>
       </c>
       <c r="O76" t="n">
         <v>3</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>12.67</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45793</v>
+        <v>45796</v>
       </c>
       <c r="H77" t="n">
-        <v>93.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I77" t="n">
         <v>95.26663330689368</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.69</v>
+        <v>-6.81</v>
       </c>
       <c r="L77" t="n">
-        <v>6.09</v>
+        <v>8.91</v>
       </c>
       <c r="M77" t="n">
         <v>3.85</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H78" t="n">
-        <v>99.61</v>
+        <v>97.25</v>
       </c>
       <c r="I78" t="n">
         <v>98.68120308140736</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K78" t="n">
-        <v>4.52</v>
+        <v>2.05</v>
       </c>
       <c r="L78" t="n">
         <v>1.9</v>
@@ -4887,7 +5822,7 @@
         <v>2.61</v>
       </c>
       <c r="N78" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="O78" t="n">
         <v>2.03</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>8.57</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="H79" t="n">
-        <v>103.34</v>
+        <v>107.38</v>
       </c>
       <c r="I79" t="n">
         <v>105.5891621503924</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>-6.26</v>
+        <v>-10.42</v>
       </c>
       <c r="L79" t="n">
-        <v>8.4</v>
+        <v>10.56</v>
       </c>
       <c r="M79" t="n">
         <v>1.13</v>
       </c>
       <c r="N79" t="n">
-        <v>2.96</v>
+        <v>3.91</v>
       </c>
       <c r="O79" t="n">
         <v>-2.37</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,25 +5939,25 @@
         <v>8.6</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="H80" t="n">
-        <v>105.05</v>
+        <v>102.4</v>
       </c>
       <c r="I80" t="n">
         <v>103.7340114047799</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.17</v>
+        <v>-4.64</v>
       </c>
       <c r="L80" t="n">
-        <v>3.85</v>
+        <v>5.96</v>
       </c>
       <c r="M80" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="N80" t="n">
         <v>3.17</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H81" t="n">
-        <v>103.26</v>
+        <v>104.72</v>
       </c>
       <c r="I81" t="n">
         <v>104.3718758151568</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.84</v>
+        <v>-2.27</v>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="M81" t="n">
         <v>0.68</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>5.53</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H82" t="n">
-        <v>118.27</v>
+        <v>112.72</v>
       </c>
       <c r="I82" t="n">
         <v>115.81220726135</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K82" t="n">
-        <v>12.94</v>
+        <v>7.64</v>
       </c>
       <c r="L82" t="n">
         <v>1.4</v>
@@ -5115,7 +6098,7 @@
         <v>0.48</v>
       </c>
       <c r="N82" t="n">
-        <v>4.43</v>
+        <v>4.69</v>
       </c>
       <c r="O82" t="n">
         <v>1.41</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4</v>
+      </c>
+      <c r="U82" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>10.14</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="H83" t="n">
-        <v>121</v>
+        <v>125.04</v>
       </c>
       <c r="I83" t="n">
         <v>122.2168182444649</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K83" t="n">
-        <v>-7.35</v>
+        <v>-10.93</v>
       </c>
       <c r="L83" t="n">
-        <v>10.56</v>
+        <v>11.2</v>
       </c>
       <c r="M83" t="n">
         <v>0.53</v>
       </c>
       <c r="N83" t="n">
-        <v>1.97</v>
+        <v>3.34</v>
       </c>
       <c r="O83" t="n">
         <v>-4.69</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>7.75</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="H84" t="n">
-        <v>121.62</v>
+        <v>116.75</v>
       </c>
       <c r="I84" t="n">
         <v>118.7728314774818</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K84" t="n">
-        <v>-2.74</v>
+        <v>-6.63</v>
       </c>
       <c r="L84" t="n">
-        <v>4.57</v>
+        <v>7.09</v>
       </c>
       <c r="M84" t="n">
         <v>0.38</v>
       </c>
       <c r="N84" t="n">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="O84" t="n">
         <v>3.34</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>12.25</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="H85" t="n">
-        <v>122.54</v>
+        <v>125.93</v>
       </c>
       <c r="I85" t="n">
         <v>124.985846316262</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K85" t="n">
-        <v>-4.96</v>
+        <v>-7.86</v>
       </c>
       <c r="L85" t="n">
-        <v>7.37</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M85" t="n">
         <v>3.68</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,22 +6353,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="H86" t="n">
-        <v>118.75</v>
+        <v>115.94</v>
       </c>
       <c r="I86" t="n">
         <v>117.4518111915149</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K86" t="n">
-        <v>-5.7</v>
+        <v>-7.93</v>
       </c>
       <c r="L86" t="n">
-        <v>7.25</v>
+        <v>8.43</v>
       </c>
       <c r="M86" t="n">
         <v>3.39</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>9.98</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H87" t="n">
-        <v>110.35</v>
+        <v>111.25</v>
       </c>
       <c r="I87" t="n">
         <v>111.249624325577</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K87" t="n">
-        <v>4.82</v>
+        <v>4.05</v>
       </c>
       <c r="L87" t="n">
         <v>2.56</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,28 +6491,28 @@
         <v>10.16</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H88" t="n">
-        <v>104.21</v>
+        <v>101.66</v>
       </c>
       <c r="I88" t="n">
         <v>102.3834788607382</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K88" t="n">
-        <v>-6.33</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>7.89</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M88" t="n">
         <v>1.21</v>
       </c>
       <c r="N88" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="O88" t="n">
         <v>0.82</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5493,28 +6560,28 @@
         <v>9.43</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H89" t="n">
-        <v>102.72</v>
+        <v>106.55</v>
       </c>
       <c r="I89" t="n">
         <v>105.6303573236623</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K89" t="n">
-        <v>-1.04</v>
+        <v>-4.81</v>
       </c>
       <c r="L89" t="n">
-        <v>4</v>
+        <v>5.12</v>
       </c>
       <c r="M89" t="n">
         <v>0.98</v>
       </c>
       <c r="N89" t="n">
-        <v>3.51</v>
+        <v>3.73</v>
       </c>
       <c r="O89" t="n">
         <v>-2.45</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5550,28 +6629,28 @@
         <v>9.07</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="H90" t="n">
-        <v>103.79</v>
+        <v>100.95</v>
       </c>
       <c r="I90" t="n">
         <v>102.4587276881721</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K90" t="n">
-        <v>-2.59</v>
+        <v>-5.26</v>
       </c>
       <c r="L90" t="n">
-        <v>4.13</v>
+        <v>5.73</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="O90" t="n">
         <v>3.73</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5607,28 +6698,28 @@
         <v>7.38</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H91" t="n">
-        <v>105.77</v>
+        <v>111.76</v>
       </c>
       <c r="I91" t="n">
         <v>108.4032951770524</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K91" t="n">
-        <v>-4.77</v>
+        <v>-10.71</v>
       </c>
       <c r="L91" t="n">
-        <v>6.54</v>
+        <v>10.9</v>
       </c>
       <c r="M91" t="n">
-        <v>0.64</v>
+        <v>2.35</v>
       </c>
       <c r="N91" t="n">
-        <v>2.47</v>
+        <v>5.66</v>
       </c>
       <c r="O91" t="n">
         <v>-2.74</v>
@@ -5637,7 +6728,19 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5664,19 +6767,19 @@
         <v>8.73</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H92" t="n">
-        <v>112.6</v>
+        <v>111.75</v>
       </c>
       <c r="I92" t="n">
         <v>112.093837795266</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K92" t="n">
-        <v>0.75</v>
+        <v>-0.01</v>
       </c>
       <c r="L92" t="n">
         <v>3.9</v>
@@ -5694,7 +6797,19 @@
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>3</v>
+      </c>
+      <c r="U92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -5721,28 +6836,28 @@
         <v>7.06</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="H93" t="n">
-        <v>116.3</v>
+        <v>121.9</v>
       </c>
       <c r="I93" t="n">
         <v>119.3989491781389</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K93" t="n">
-        <v>-4.07</v>
+        <v>-9.08</v>
       </c>
       <c r="L93" t="n">
-        <v>7.06</v>
+        <v>12.05</v>
       </c>
       <c r="M93" t="n">
-        <v>1.08</v>
+        <v>3.93</v>
       </c>
       <c r="N93" t="n">
-        <v>2.54</v>
+        <v>4.82</v>
       </c>
       <c r="O93" t="n">
         <v>-0.75</v>
@@ -5751,7 +6866,19 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S93" t="b">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5802,6 +6929,14 @@
       <c r="Q94" t="n">
         <v>7</v>
       </c>
+      <c r="R94" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10760,7 +11895,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="6">
@@ -10770,7 +11905,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -10780,7 +11915,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -10790,7 +11925,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -10800,7 +11935,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57.2</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="10">
@@ -10810,7 +11945,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90.5</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -10820,7 +11955,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -10830,7 +11965,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -10840,7 +11975,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43.5</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="14">
@@ -10850,7 +11985,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.68</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="15">
@@ -10860,7 +11995,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.02</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="16">
@@ -10870,7 +12005,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.33</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="17">
@@ -10880,7 +12015,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53.22</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -10890,7 +12025,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.6</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="19">
@@ -10900,7 +12035,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.62</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -10910,7 +12045,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.02</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -10920,7 +12055,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.77</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="22">
@@ -10930,7 +12065,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
@@ -10940,7 +12075,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -10950,7 +12085,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="25">
@@ -10960,7 +12095,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.93</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="26">
@@ -10970,7 +12105,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.72</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="27">
@@ -10980,7 +12115,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.83</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="28">
@@ -10990,7 +12125,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
